--- a/src/assets/excels/员工名单.xlsx
+++ b/src/assets/excels/员工名单.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codes\private\party-lottery\src\assets\excels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16870" windowHeight="17080"/>
+    <workbookView windowWidth="20200" windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="124">
   <si>
     <t>employeeId</t>
   </si>
@@ -142,7 +147,7 @@
     <t>赵贞吉</t>
   </si>
   <si>
-    <t>南直隶 户部 内阁</t>
+    <t>南直隶巡抚署 户部 内阁</t>
   </si>
   <si>
     <t>000012</t>
@@ -151,7 +156,7 @@
     <t>胡宗宪</t>
   </si>
   <si>
-    <t>兵部 浙直总督府</t>
+    <t>兵部 浙江巡抚署 浙直总督府</t>
   </si>
   <si>
     <t>000013</t>
@@ -178,7 +183,7 @@
     <t>王用汲</t>
   </si>
   <si>
-    <t>昆山县 建德县</t>
+    <t>昆山县 建德县 都察院</t>
   </si>
   <si>
     <t>000016</t>
@@ -196,7 +201,7 @@
     <t>郑必昌</t>
   </si>
   <si>
-    <t>浙江巡抚 浙江布政使司</t>
+    <t>浙江巡抚署 浙江布政使司</t>
   </si>
   <si>
     <t>000018</t>
@@ -205,7 +210,7 @@
     <t>何茂才</t>
   </si>
   <si>
-    <t>浙江布政使司 浙江按察使司</t>
+    <t>浙江按察使司 浙江布政使司</t>
   </si>
   <si>
     <t>000019</t>
@@ -235,7 +240,7 @@
     <t>杨金水</t>
   </si>
   <si>
-    <t>浙江市舶司</t>
+    <t>江南织造局浙江市舶司</t>
   </si>
   <si>
     <t>000023</t>
@@ -371,6 +376,36 @@
   </si>
   <si>
     <t>国子监</t>
+  </si>
+  <si>
+    <t>000039</t>
+  </si>
+  <si>
+    <t>李玄</t>
+  </si>
+  <si>
+    <t>河道衙门</t>
+  </si>
+  <si>
+    <t>000040</t>
+  </si>
+  <si>
+    <t>石公公</t>
+  </si>
+  <si>
+    <t>000041</t>
+  </si>
+  <si>
+    <t>孟公公</t>
+  </si>
+  <si>
+    <t>000042</t>
+  </si>
+  <si>
+    <t>徐璠</t>
+  </si>
+  <si>
+    <t>工部</t>
   </si>
 </sst>
 </file>
@@ -1314,7 +1349,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="13.8181818181818" customWidth="1"/>
@@ -1787,6 +1822,50 @@
       </c>
       <c r="C39" t="s">
         <v>113</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B40" t="s">
+        <v>115</v>
+      </c>
+      <c r="C40" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B41" t="s">
+        <v>118</v>
+      </c>
+      <c r="C41" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B42" t="s">
+        <v>120</v>
+      </c>
+      <c r="C42" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B43" t="s">
+        <v>122</v>
+      </c>
+      <c r="C43" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/src/assets/excels/员工名单.xlsx
+++ b/src/assets/excels/员工名单.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20200" windowHeight="17680"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="172">
   <si>
     <t>employeeId</t>
   </si>
@@ -75,10 +75,16 @@
     <t>皇室</t>
   </si>
   <si>
+    <t>https://bkimg.cdn.bcebos.com/pic/242dd42a2834349b5243af86c6ea15ce36d3be68?x-bce-process=image/format,f_auto/watermark,image_d2F0ZXIvYmFpa2UyNzI,g_7,xp_5,yp_5,P_20/resize,m_lfit,limit_1,h_1080</t>
+  </si>
+  <si>
     <t>000002</t>
   </si>
   <si>
-    <t>朱载垕</t>
+    <t>朱载坖</t>
+  </si>
+  <si>
+    <t>http://k.sinaimg.cn/n/sinacn10106/155/w640h315/20200229/5b0c-iqfqmas5532957.jpg/w700d1q75cms.jpg</t>
   </si>
   <si>
     <t>000003</t>
@@ -87,6 +93,9 @@
     <t>朱翊钧</t>
   </si>
   <si>
+    <t>https://pics4.baidu.com/feed/d0c8a786c9177f3e3e81c42cb86eb5d79e3d568f.jpeg@f_auto?token=a26146de77392b2cf57e9ae363d0dab0</t>
+  </si>
+  <si>
     <t>000004</t>
   </si>
   <si>
@@ -96,6 +105,9 @@
     <t>内阁</t>
   </si>
   <si>
+    <t>https://pics3.baidu.com/feed/9f510fb30f2442a78cf239bf109e4c5bd013021e.jpeg@f_auto?token=ed160534423d78057f892d2ccc1ca56f</t>
+  </si>
+  <si>
     <t>000005</t>
   </si>
   <si>
@@ -105,6 +117,9 @@
     <t>内阁 户部</t>
   </si>
   <si>
+    <t>https://pic.rmb.bdstatic.com/bjh/events/24cfb80c8e95f3fbca04251e633b4d211187.jpeg@h_1280</t>
+  </si>
+  <si>
     <t>000006</t>
   </si>
   <si>
@@ -120,6 +135,9 @@
     <t>高拱</t>
   </si>
   <si>
+    <t>https://pic.rmb.bdstatic.com/bjh/cms/251211/c9400d9481b8bef0d2089acc0dcb5d4f_1765419986.2928_769.jpeg</t>
+  </si>
+  <si>
     <t>000008</t>
   </si>
   <si>
@@ -129,12 +147,18 @@
     <t>内阁 兵部</t>
   </si>
   <si>
+    <t>https://img1.baidu.com/it/u=1932781326,3970607845&amp;fm=253&amp;app=138&amp;f=JPEG?w=969&amp;h=568</t>
+  </si>
+  <si>
     <t>000009</t>
   </si>
   <si>
     <t>李春芳</t>
   </si>
   <si>
+    <t>https://pic.rmb.bdstatic.com/bjh/cms/251211/061a156c6956be94fdbf37150ef1595c_1765419986.5345_962.jpeg</t>
+  </si>
+  <si>
     <t>000010</t>
   </si>
   <si>
@@ -150,6 +174,9 @@
     <t>南直隶巡抚署 户部 内阁</t>
   </si>
   <si>
+    <t>https://pics6.baidu.com/feed/6609c93d70cf3bc7e75fd9dbe2a04eb1cc112ade.jpeg@f_auto?token=45a1a302848dc17141270ce838a263e3</t>
+  </si>
+  <si>
     <t>000012</t>
   </si>
   <si>
@@ -159,6 +186,9 @@
     <t>兵部 浙江巡抚署 浙直总督府</t>
   </si>
   <si>
+    <t>https://pics7.baidu.com/feed/c8ea15ce36d3d5398ae6732637e42156372ab0e1.jpeg?token=70833c4198ded231e9d58c967d618804</t>
+  </si>
+  <si>
     <t>000013</t>
   </si>
   <si>
@@ -168,6 +198,9 @@
     <t>裕王府 浙直总督府 浙江按察使司</t>
   </si>
   <si>
+    <t>https://picx.zhimg.com/v2-e4d53f7e314afdae5ca3730c853ff29f_1440w.jpg</t>
+  </si>
+  <si>
     <t>000014</t>
   </si>
   <si>
@@ -177,6 +210,9 @@
     <t>南平县 淳安县 兴国县 户部</t>
   </si>
   <si>
+    <t>https://pica.zhimg.com/v2-af840f38b82d93c931fff1ed6c98525e_r.jpg</t>
+  </si>
+  <si>
     <t>000015</t>
   </si>
   <si>
@@ -186,6 +222,9 @@
     <t>昆山县 建德县 都察院</t>
   </si>
   <si>
+    <t>https://img2.baidu.com/it/u=1889298490,2559548099&amp;fm=253&amp;app=138&amp;f=JPEG?w=800&amp;h=1065</t>
+  </si>
+  <si>
     <t>000016</t>
   </si>
   <si>
@@ -195,6 +234,9 @@
     <t>翰林院 杭州府</t>
   </si>
   <si>
+    <t>https://p5.itc.cn/images01/20210725/168e093bd60d4db9b1da751bc09869df.jpeg</t>
+  </si>
+  <si>
     <t>000017</t>
   </si>
   <si>
@@ -204,6 +246,9 @@
     <t>浙江巡抚署 浙江布政使司</t>
   </si>
   <si>
+    <t>https://5b0988e595225.cdn.sohucs.com/images/20191127/bc38c7c521b14ba2baf63c932cd48742.jpeg</t>
+  </si>
+  <si>
     <t>000018</t>
   </si>
   <si>
@@ -213,6 +258,9 @@
     <t>浙江按察使司 浙江布政使司</t>
   </si>
   <si>
+    <t>https://pic4.zhimg.com/v2-ba6876a60f9dc8147e5af8c603190159_r.jpg</t>
+  </si>
+  <si>
     <t>000019</t>
   </si>
   <si>
@@ -222,18 +270,27 @@
     <t>司礼监</t>
   </si>
   <si>
+    <t>https://pic.rmb.bdstatic.com/bjh/events/9247bf63ce76c1566fd4a87604b4137b.jpeg@h_1280</t>
+  </si>
+  <si>
     <t>000020</t>
   </si>
   <si>
     <t>陈洪</t>
   </si>
   <si>
+    <t>https://bj.bcebos.com/bjh-pixel/17074404270947698282_0_ainote_new.jpg</t>
+  </si>
+  <si>
     <t>000021</t>
   </si>
   <si>
     <t>黄锦</t>
   </si>
   <si>
+    <t>https://pica.zhimg.com/v2-3aaacfb766f01fbb7af337f709683413_r.jpg?source=1def8aca</t>
+  </si>
+  <si>
     <t>000022</t>
   </si>
   <si>
@@ -243,6 +300,9 @@
     <t>江南织造局浙江市舶司</t>
   </si>
   <si>
+    <t>https://bkimg.cdn.bcebos.com/pic/4ec2d5628535e5dd6ca87edc79c6a7efce1b6229?x-bce-process=image/format,f_auto/watermark,image_d2F0ZXIvYmFpa2UyNzI,g_7,xp_5,yp_5,P_20/resize,m_lfit,limit_1,h_1080</t>
+  </si>
+  <si>
     <t>000023</t>
   </si>
   <si>
@@ -252,6 +312,9 @@
     <t>东缉事厂 裕王府</t>
   </si>
   <si>
+    <t>https://q2.itc.cn/images01/20240318/00b7e1c04ec74a1bbc5c9672805c10bc.png</t>
+  </si>
+  <si>
     <t>000024</t>
   </si>
   <si>
@@ -261,6 +324,9 @@
     <t>钦天监</t>
   </si>
   <si>
+    <t>https://pic.rmb.bdstatic.com/bjh/news/5a389364e2a9b1ce829654808e56490d.jpeg@wm_2,t_55m+5a625Y+3L+S6jOWNgeS6jOeUu+WQmw==,fc_ffffff,ff_U2ltSGVp,sz_44,x_28,y_28</t>
+  </si>
+  <si>
     <t>000025</t>
   </si>
   <si>
@@ -270,6 +336,9 @@
     <t>台州府</t>
   </si>
   <si>
+    <t>https://p3.itc.cn/images01/20200713/e40f18569c1f47b9a6607909d0f9661a.jpeg</t>
+  </si>
+  <si>
     <t>000026</t>
   </si>
   <si>
@@ -279,6 +348,9 @@
     <t>杭州府</t>
   </si>
   <si>
+    <t>https://pic.rmb.bdstatic.com/5fdacac31c40f7944002be17c6aa2b9b.jpeg@c_1,w_653,h_508,x_0,y_15</t>
+  </si>
+  <si>
     <t>000027</t>
   </si>
   <si>
@@ -306,6 +378,9 @@
     <t>北镇抚司</t>
   </si>
   <si>
+    <t>https://k.sinaimg.cn/n/sinakd10101/155/w640h315/20210622/b870-krwipar0342715.jpg/w700d1q75cms.jpg</t>
+  </si>
+  <si>
     <t>000030</t>
   </si>
   <si>
@@ -327,6 +402,9 @@
     <t>田有禄</t>
   </si>
   <si>
+    <t>https://pic.rmb.bdstatic.com/bjh/down/c73e2aa14974c1381b8101928dffef4b.jpeg</t>
+  </si>
+  <si>
     <t>000033</t>
   </si>
   <si>
@@ -336,6 +414,9 @@
     <t>浙江按察使司</t>
   </si>
   <si>
+    <t>https://img2.baidu.com/it/u=3354097714,87429070&amp;fm=253&amp;fmt=auto&amp;app=138&amp;f=JPEG?w=607&amp;h=371</t>
+  </si>
+  <si>
     <t>000034</t>
   </si>
   <si>
@@ -351,6 +432,9 @@
     <t>江南织造局</t>
   </si>
   <si>
+    <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fvideoimg.ws.126.net%2Fcover%2F20260801%2FSaZKj3XnY_cover.jpg&amp;thumbnail=668y375&amp;quality=95&amp;type=jpg</t>
+  </si>
+  <si>
     <t>000036</t>
   </si>
   <si>
@@ -378,6 +462,9 @@
     <t>国子监</t>
   </si>
   <si>
+    <t>https://pic.rmb.bdstatic.com/bjh/cms/240822/aba6580ce7eeff5e5e6c79efb0277f9f_1724307990.0533_419.jpeg</t>
+  </si>
+  <si>
     <t>000039</t>
   </si>
   <si>
@@ -387,12 +474,18 @@
     <t>河道衙门</t>
   </si>
   <si>
+    <t>https://pic.rmb.bdstatic.com/bjh/bc1ba39241b/251231/037c3ff7b593292e4e8a2e54d7b584f1.jpeg</t>
+  </si>
+  <si>
     <t>000040</t>
   </si>
   <si>
     <t>石公公</t>
   </si>
   <si>
+    <t>https://pic3.zhimg.com/v2-2cf06bf65fa8b60efe230c8591eb8a6c_1440w.jpg</t>
+  </si>
+  <si>
     <t>000041</t>
   </si>
   <si>
@@ -406,6 +499,57 @@
   </si>
   <si>
     <t>工部</t>
+  </si>
+  <si>
+    <t>https://pic.rmb.bdstatic.com/bjh/cms/240905/3669c2e74451d13d335e5068e4e5a907_1725511981.4027_581.jpeg</t>
+  </si>
+  <si>
+    <t>000043</t>
+  </si>
+  <si>
+    <t>李时珍</t>
+  </si>
+  <si>
+    <t>太医院</t>
+  </si>
+  <si>
+    <t>https://n.sinaimg.cn/sinakd20220113s/611/w593h818/20220113/b29b-b2be732d6212950695efafa8b40e60e8.jpg</t>
+  </si>
+  <si>
+    <t>000044</t>
+  </si>
+  <si>
+    <t>李侧妃</t>
+  </si>
+  <si>
+    <t>裕王府</t>
+  </si>
+  <si>
+    <t>https://q4.itc.cn/images01/20251104/d027840e814144679999799784bf3ab2.jpeg</t>
+  </si>
+  <si>
+    <t>000045</t>
+  </si>
+  <si>
+    <t>芸娘</t>
+  </si>
+  <si>
+    <t>https://t11.baidu.com/it/u=249142615,298677475&amp;fm=30&amp;app=106&amp;f=JPEG?w=640&amp;h=477&amp;s=A280D44F822ACB551E6061280300C04A</t>
+  </si>
+  <si>
+    <t>000046</t>
+  </si>
+  <si>
+    <t>000047</t>
+  </si>
+  <si>
+    <t>000048</t>
+  </si>
+  <si>
+    <t>000049</t>
+  </si>
+  <si>
+    <t>000050</t>
   </si>
 </sst>
 </file>
@@ -418,7 +562,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -427,10 +571,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9.8"/>
-      <color rgb="FF660E7A"/>
-      <name val="Courier New"/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -578,12 +728,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4F81BD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -898,55 +1054,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
@@ -961,78 +1114,90 @@
     <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
@@ -1091,6 +1256,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="004F81BD"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1349,50 +1519,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="13.8181818181818" customWidth="1"/>
-    <col min="2" max="2" width="12.6363636363636" customWidth="1"/>
-    <col min="3" max="3" width="37.0909090909091" customWidth="1"/>
-    <col min="4" max="4" width="45.2727272727273" customWidth="1"/>
-    <col min="10" max="10" width="10.8181818181818" customWidth="1"/>
+    <col min="1" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="10" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
@@ -1401,69 +1570,84 @@
       <c r="C2" t="s">
         <v>12</v>
       </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
       <c r="E2">
         <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>13</v>
+      <c r="A3" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
       </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>15</v>
+      <c r="A4" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
       </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>17</v>
+      <c r="A5" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
       </c>
       <c r="E5">
         <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>20</v>
+      <c r="A6" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
       </c>
       <c r="E6">
         <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>23</v>
+      <c r="A7" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E7">
         <v>50</v>
@@ -1473,402 +1657,555 @@
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
         <v>26</v>
       </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="D8" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>19</v>
+      <c r="D10" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>33</v>
+      <c r="A11" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>35</v>
+      <c r="A12" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>45</v>
+      </c>
+      <c r="D12" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>38</v>
+      <c r="A13" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>49</v>
+      </c>
+      <c r="D13" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>41</v>
+      <c r="A14" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>53</v>
+      </c>
+      <c r="D14" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>44</v>
+      <c r="A15" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>57</v>
+      </c>
+      <c r="D15" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>47</v>
+      <c r="A16" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
+      </c>
+      <c r="D16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>53</v>
+        <v>65</v>
+      </c>
+      <c r="D17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="5" t="s">
+        <v>67</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>56</v>
+        <v>69</v>
+      </c>
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>59</v>
+        <v>73</v>
+      </c>
+      <c r="D19" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>62</v>
+        <v>77</v>
+      </c>
+      <c r="D20" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
-        <v>64</v>
+        <v>77</v>
+      </c>
+      <c r="D21" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="2" t="s">
-        <v>66</v>
+        <v>77</v>
+      </c>
+      <c r="D22" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="2" t="s">
-        <v>69</v>
+        <v>87</v>
+      </c>
+      <c r="D23" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="2" t="s">
-        <v>72</v>
+        <v>91</v>
+      </c>
+      <c r="D24" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="2" t="s">
-        <v>75</v>
+        <v>95</v>
+      </c>
+      <c r="D25" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="B26" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s">
+        <v>99</v>
+      </c>
+      <c r="D26" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B27" t="s">
+        <v>102</v>
+      </c>
+      <c r="C27" t="s">
+        <v>103</v>
+      </c>
+      <c r="D27" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B28" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B29" t="s">
+        <v>109</v>
+      </c>
+      <c r="C29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B30" t="s">
+        <v>112</v>
+      </c>
+      <c r="C30" t="s">
+        <v>113</v>
+      </c>
+      <c r="D30" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C31" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B32" t="s">
+        <v>118</v>
+      </c>
+      <c r="C32" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B33" t="s">
+        <v>121</v>
+      </c>
+      <c r="C33" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B34" t="s">
+        <v>124</v>
+      </c>
+      <c r="C34" t="s">
+        <v>125</v>
+      </c>
+      <c r="D34" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B35" t="s">
+        <v>128</v>
+      </c>
+      <c r="C35" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B36" t="s">
+        <v>130</v>
+      </c>
+      <c r="C36" t="s">
+        <v>131</v>
+      </c>
+      <c r="D36" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B37" t="s">
+        <v>134</v>
+      </c>
+      <c r="C37" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B38" t="s">
+        <v>137</v>
+      </c>
+      <c r="C38" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B39" t="s">
+        <v>140</v>
+      </c>
+      <c r="C39" t="s">
+        <v>141</v>
+      </c>
+      <c r="D39" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B40" t="s">
+        <v>144</v>
+      </c>
+      <c r="C40" t="s">
+        <v>145</v>
+      </c>
+      <c r="D40" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B41" t="s">
+        <v>148</v>
+      </c>
+      <c r="C41" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B27" t="s">
-        <v>79</v>
-      </c>
-      <c r="C27" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B28" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B29" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="2" t="s">
+      <c r="D41" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B42" t="s">
+        <v>151</v>
+      </c>
+      <c r="C42" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B43" t="s">
+        <v>153</v>
+      </c>
+      <c r="C43" t="s">
+        <v>154</v>
+      </c>
+      <c r="D43" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B44" t="s">
+        <v>157</v>
+      </c>
+      <c r="C44" t="s">
+        <v>158</v>
+      </c>
+      <c r="D44" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B45" t="s">
+        <v>161</v>
+      </c>
+      <c r="C45" t="s">
+        <v>162</v>
+      </c>
+      <c r="D45" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B46" t="s">
+        <v>165</v>
+      </c>
+      <c r="C46" t="s">
         <v>87</v>
       </c>
-      <c r="B30" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B31" t="s">
-        <v>91</v>
-      </c>
-      <c r="C31" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B32" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B33" t="s">
-        <v>96</v>
-      </c>
-      <c r="C33" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B34" t="s">
-        <v>98</v>
-      </c>
-      <c r="C34" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B35" t="s">
-        <v>101</v>
-      </c>
-      <c r="C35" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B36" t="s">
-        <v>103</v>
-      </c>
-      <c r="C36" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B37" t="s">
-        <v>106</v>
-      </c>
-      <c r="C37" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B38" t="s">
-        <v>109</v>
-      </c>
-      <c r="C38" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B39" t="s">
-        <v>112</v>
-      </c>
-      <c r="C39" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B40" t="s">
-        <v>115</v>
-      </c>
-      <c r="C40" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B41" t="s">
-        <v>118</v>
-      </c>
-      <c r="C41" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B42" t="s">
-        <v>120</v>
-      </c>
-      <c r="C42" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B43" t="s">
-        <v>122</v>
-      </c>
-      <c r="C43" t="s">
-        <v>123</v>
+      <c r="D46" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="5" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D9" r:id="rId1" display="https://img1.baidu.com/it/u=1932781326,3970607845&amp;fm=253&amp;app=138&amp;f=JPEG?w=969&amp;h=568"/>
+    <hyperlink ref="D8" r:id="rId2" display="https://pic.rmb.bdstatic.com/bjh/cms/251211/c9400d9481b8bef0d2089acc0dcb5d4f_1765419986.2928_769.jpeg"/>
+    <hyperlink ref="D10" r:id="rId3" display="https://pic.rmb.bdstatic.com/bjh/cms/251211/061a156c6956be94fdbf37150ef1595c_1765419986.5345_962.jpeg"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/src/assets/excels/员工名单.xlsx
+++ b/src/assets/excels/员工名单.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="175">
   <si>
     <t>employeeId</t>
   </si>
@@ -75,7 +75,7 @@
     <t>皇室</t>
   </si>
   <si>
-    <t>https://bkimg.cdn.bcebos.com/pic/242dd42a2834349b5243af86c6ea15ce36d3be68?x-bce-process=image/format,f_auto/watermark,image_d2F0ZXIvYmFpa2UyNzI,g_7,xp_5,yp_5,P_20/resize,m_lfit,limit_1,h_1080</t>
+    <t>https://i1.hdslb.com/bfs/archive/3d9709cb7d30d65583bf443a3e712f98e6976c8c.jpg</t>
   </si>
   <si>
     <t>000002</t>
@@ -183,10 +183,10 @@
     <t>胡宗宪</t>
   </si>
   <si>
-    <t>兵部 浙江巡抚署 浙直总督府</t>
-  </si>
-  <si>
-    <t>https://pics7.baidu.com/feed/c8ea15ce36d3d5398ae6732637e42156372ab0e1.jpeg?token=70833c4198ded231e9d58c967d618804</t>
+    <t>兵部 浙江巡抚署 浙直总督署</t>
+  </si>
+  <si>
+    <t>https://pic4.zhimg.com/v2-5826144298f140ca238949087e9c14a3_r.jpg</t>
   </si>
   <si>
     <t>000013</t>
@@ -195,7 +195,7 @@
     <t>谭伦</t>
   </si>
   <si>
-    <t>裕王府 浙直总督府 浙江按察使司</t>
+    <t>裕王府 浙直总督署 浙江按察使司</t>
   </si>
   <si>
     <t>https://picx.zhimg.com/v2-e4d53f7e314afdae5ca3730c853ff29f_1440w.jpg</t>
@@ -222,7 +222,7 @@
     <t>昆山县 建德县 都察院</t>
   </si>
   <si>
-    <t>https://img2.baidu.com/it/u=1889298490,2559548099&amp;fm=253&amp;app=138&amp;f=JPEG?w=800&amp;h=1065</t>
+    <t>https://i0.hdslb.com/bfs/archive/df3863c962c3374e7a21544940831a4412634925.jpg@1200w_630h</t>
   </si>
   <si>
     <t>000016</t>
@@ -333,7 +333,7 @@
     <t>戚继光</t>
   </si>
   <si>
-    <t>台州府</t>
+    <t>台州卫</t>
   </si>
   <si>
     <t>https://p3.itc.cn/images01/20200713/e40f18569c1f47b9a6607909d0f9661a.jpeg</t>
@@ -393,7 +393,7 @@
     <t>齐大柱</t>
   </si>
   <si>
-    <t>台州府 北镇抚司</t>
+    <t>台州卫 北镇抚司</t>
   </si>
   <si>
     <t>000032</t>
@@ -429,10 +429,7 @@
     <t>沈一石</t>
   </si>
   <si>
-    <t>江南织造局</t>
-  </si>
-  <si>
-    <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fvideoimg.ws.126.net%2Fcover%2F20260801%2FSaZKj3XnY_cover.jpg&amp;thumbnail=668y375&amp;quality=95&amp;type=jpg</t>
+    <t>https://i1.hdslb.com/bfs/archive/48a28178cf3787ff65505f8271489e858e40bb61.jpg</t>
   </si>
   <si>
     <t>000036</t>
@@ -474,7 +471,7 @@
     <t>河道衙门</t>
   </si>
   <si>
-    <t>https://pic.rmb.bdstatic.com/bjh/bc1ba39241b/251231/037c3ff7b593292e4e8a2e54d7b584f1.jpeg</t>
+    <t>https://bj.bcebos.com/bjh-pixel/17095232360135075178_1_ainote_new.jpg</t>
   </si>
   <si>
     <t>000040</t>
@@ -492,6 +489,9 @@
     <t>孟公公</t>
   </si>
   <si>
+    <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2024%2F0207%2Fd9497187j00s8hhs601pod001kw00u8m.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
+  </si>
+  <si>
     <t>000042</t>
   </si>
   <si>
@@ -538,6 +538,15 @@
   </si>
   <si>
     <t>000046</t>
+  </si>
+  <si>
+    <t>井上十四郎</t>
+  </si>
+  <si>
+    <t>倭寇海盗组织</t>
+  </si>
+  <si>
+    <t>https://pic1.zhimg.com/100/v2-f24f52ac6431f4cbc0e7dae9e026ddfa_r.jpg</t>
   </si>
   <si>
     <t>000047</t>
@@ -1570,7 +1579,7 @@
       <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E2">
@@ -1733,7 +1742,7 @@
       <c r="C13" t="s">
         <v>49</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="3" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1775,7 +1784,7 @@
       <c r="C16" t="s">
         <v>61</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="3" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2038,85 +2047,88 @@
         <v>130</v>
       </c>
       <c r="C36" t="s">
+        <v>87</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="D36" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B37" t="s">
         <v>133</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>134</v>
-      </c>
-      <c r="C37" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B38" t="s">
         <v>136</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>137</v>
-      </c>
-      <c r="C38" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B39" t="s">
         <v>139</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>140</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>141</v>
-      </c>
-      <c r="D39" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B40" t="s">
         <v>143</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>144</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="D40" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B41" t="s">
         <v>147</v>
-      </c>
-      <c r="B41" t="s">
-        <v>148</v>
       </c>
       <c r="C41" t="s">
         <v>77</v>
       </c>
       <c r="D41" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B42" t="s">
         <v>150</v>
-      </c>
-      <c r="B42" t="s">
-        <v>151</v>
       </c>
       <c r="C42" t="s">
         <v>77</v>
+      </c>
+      <c r="D42" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2179,25 +2191,34 @@
       <c r="A47" s="5" t="s">
         <v>167</v>
       </c>
+      <c r="B47" t="s">
+        <v>168</v>
+      </c>
+      <c r="C47" t="s">
+        <v>169</v>
+      </c>
+      <c r="D47" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="5" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="5" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="5" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -2205,6 +2226,11 @@
     <hyperlink ref="D9" r:id="rId1" display="https://img1.baidu.com/it/u=1932781326,3970607845&amp;fm=253&amp;app=138&amp;f=JPEG?w=969&amp;h=568"/>
     <hyperlink ref="D8" r:id="rId2" display="https://pic.rmb.bdstatic.com/bjh/cms/251211/c9400d9481b8bef0d2089acc0dcb5d4f_1765419986.2928_769.jpeg"/>
     <hyperlink ref="D10" r:id="rId3" display="https://pic.rmb.bdstatic.com/bjh/cms/251211/061a156c6956be94fdbf37150ef1595c_1765419986.5345_962.jpeg"/>
+    <hyperlink ref="D36" r:id="rId4" display="https://i1.hdslb.com/bfs/archive/48a28178cf3787ff65505f8271489e858e40bb61.jpg"/>
+    <hyperlink ref="D16" r:id="rId5" display="https://i0.hdslb.com/bfs/archive/df3863c962c3374e7a21544940831a4412634925.jpg@1200w_630h"/>
+    <hyperlink ref="D13" r:id="rId6" display="https://pic4.zhimg.com/v2-5826144298f140ca238949087e9c14a3_r.jpg"/>
+    <hyperlink ref="D2" r:id="rId7" display="https://i1.hdslb.com/bfs/archive/3d9709cb7d30d65583bf443a3e712f98e6976c8c.jpg"/>
+    <hyperlink ref="D40" r:id="rId8" display="https://bj.bcebos.com/bjh-pixel/17095232360135075178_1_ainote_new.jpg"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
